--- a/projects/NZIPL/docs/trade_data/latest_2024/NZIPL_2024_CountryTotals_Exports_USDmn.xlsx
+++ b/projects/NZIPL/docs/trade_data/latest_2024/NZIPL_2024_CountryTotals_Exports_USDmn.xlsx
@@ -94,7 +94,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-10</t>
+    <t xml:space="preserve">2026-07-11</t>
   </si>
   <si>
     <t xml:space="preserve">ISO3</t>
@@ -1560,7 +1560,7 @@
         <v>28</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>114038.122</v>
+        <v>115213.782</v>
       </c>
     </row>
     <row r="3">
@@ -1571,7 +1571,7 @@
         <v>34</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>63524.425</v>
+        <v>63568.11</v>
       </c>
     </row>
     <row r="4">
@@ -1582,7 +1582,7 @@
         <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>69101.557</v>
+        <v>70013.879</v>
       </c>
     </row>
     <row r="5">
@@ -1593,7 +1593,7 @@
         <v>36</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>30025.779</v>
+        <v>30026.753</v>
       </c>
     </row>
     <row r="6">
@@ -1604,7 +1604,7 @@
         <v>44</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>25615.538</v>
+        <v>25620.207</v>
       </c>
     </row>
     <row r="7">
@@ -1615,7 +1615,7 @@
         <v>46</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>17251.128</v>
+        <v>17344.166</v>
       </c>
     </row>
     <row r="8">
@@ -1626,7 +1626,7 @@
         <v>38</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>22654.119</v>
+        <v>22657.109</v>
       </c>
     </row>
     <row r="9">
@@ -1637,7 +1637,7 @@
         <v>42</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>19691.33</v>
+        <v>19691.767</v>
       </c>
     </row>
     <row r="10">
@@ -1648,7 +1648,7 @@
         <v>60</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>23524.128</v>
+        <v>23542.409</v>
       </c>
     </row>
     <row r="11">
@@ -1659,7 +1659,7 @@
         <v>48</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>12719.761</v>
+        <v>12740.036</v>
       </c>
     </row>
     <row r="12">
@@ -1670,7 +1670,7 @@
         <v>50</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>15000.578</v>
+        <v>15010.719</v>
       </c>
     </row>
     <row r="13">
@@ -1681,7 +1681,7 @@
         <v>64</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>13483.178</v>
+        <v>13760.561</v>
       </c>
     </row>
     <row r="14">
@@ -1692,7 +1692,7 @@
         <v>58</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>9134.998</v>
+        <v>9135.609</v>
       </c>
     </row>
     <row r="15">
@@ -1703,7 +1703,7 @@
         <v>30</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>20594.267</v>
+        <v>20594.321</v>
       </c>
     </row>
     <row r="16">
@@ -1714,7 +1714,7 @@
         <v>54</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>17432.358</v>
+        <v>17634.532</v>
       </c>
     </row>
     <row r="17">
@@ -1725,7 +1725,7 @@
         <v>56</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>9486.744</v>
+        <v>9490.023</v>
       </c>
     </row>
     <row r="18">
@@ -1758,7 +1758,7 @@
         <v>74</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>13040.795</v>
+        <v>13045.296</v>
       </c>
     </row>
     <row r="21">
@@ -1769,7 +1769,7 @@
         <v>40</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>12106.031</v>
+        <v>12110.881</v>
       </c>
     </row>
     <row r="22">
@@ -1780,7 +1780,7 @@
         <v>88</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>8708.483</v>
+        <v>8708.815</v>
       </c>
     </row>
     <row r="23">
@@ -1791,29 +1791,29 @@
         <v>84</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>8544.951</v>
+        <v>8548.036</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>6579.631</v>
+        <v>7676.407</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>7676.009</v>
+        <v>6580.253</v>
       </c>
     </row>
     <row r="26">
@@ -1824,7 +1824,7 @@
         <v>86</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>10713.984</v>
+        <v>10716.826</v>
       </c>
     </row>
     <row r="27">
@@ -1835,7 +1835,7 @@
         <v>92</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>8292.05</v>
+        <v>8293.106</v>
       </c>
     </row>
     <row r="28">
@@ -1857,7 +1857,7 @@
         <v>70</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>10295.166</v>
+        <v>10295.299</v>
       </c>
     </row>
     <row r="30">
@@ -1917,7 +1917,7 @@
         <v>28</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>81856.718</v>
+        <v>82237.343</v>
       </c>
     </row>
     <row r="3">
@@ -1928,7 +1928,7 @@
         <v>30</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>101649.987</v>
+        <v>101651.756</v>
       </c>
     </row>
     <row r="4">
@@ -1939,7 +1939,7 @@
         <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>35293.432</v>
+        <v>35320.896</v>
       </c>
     </row>
     <row r="5">
@@ -1950,7 +1950,7 @@
         <v>34</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>33343.912</v>
+        <v>33383.677</v>
       </c>
     </row>
     <row r="6">
@@ -1961,7 +1961,7 @@
         <v>36</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>17607.346</v>
+        <v>17662.524</v>
       </c>
     </row>
     <row r="7">
@@ -1972,7 +1972,7 @@
         <v>38</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>19944.506</v>
+        <v>19951.898</v>
       </c>
     </row>
     <row r="8">
@@ -1994,7 +1994,7 @@
         <v>42</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>16194.005</v>
+        <v>16199.681</v>
       </c>
     </row>
     <row r="10">
@@ -2005,7 +2005,7 @@
         <v>44</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>9700.643</v>
+        <v>9713.349</v>
       </c>
     </row>
     <row r="11">
@@ -2016,7 +2016,7 @@
         <v>46</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>7018.087</v>
+        <v>7041.005</v>
       </c>
     </row>
     <row r="12">
@@ -2027,7 +2027,7 @@
         <v>48</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>6421.481</v>
+        <v>6429.162</v>
       </c>
     </row>
     <row r="13">
@@ -2038,7 +2038,7 @@
         <v>50</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>7906.511</v>
+        <v>7921.423</v>
       </c>
     </row>
     <row r="14">
@@ -2049,7 +2049,7 @@
         <v>52</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>35826.888</v>
+        <v>35827.075</v>
       </c>
     </row>
     <row r="15">
@@ -2060,7 +2060,7 @@
         <v>54</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>6808.851</v>
+        <v>6814.14</v>
       </c>
     </row>
     <row r="16">
@@ -2071,7 +2071,7 @@
         <v>56</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>5834.882</v>
+        <v>5842.254</v>
       </c>
     </row>
     <row r="17">
@@ -2082,7 +2082,7 @@
         <v>58</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>4823.16</v>
+        <v>4830.35</v>
       </c>
     </row>
     <row r="18">
@@ -2093,7 +2093,7 @@
         <v>60</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>7441.012</v>
+        <v>7441.759</v>
       </c>
     </row>
     <row r="19">
@@ -2104,7 +2104,7 @@
         <v>62</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>19525.95</v>
+        <v>19537.278</v>
       </c>
     </row>
     <row r="20">
@@ -2115,7 +2115,7 @@
         <v>64</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>5149.582</v>
+        <v>5160.107</v>
       </c>
     </row>
     <row r="21">
@@ -2126,7 +2126,7 @@
         <v>66</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>4536.756</v>
+        <v>4539.238</v>
       </c>
     </row>
     <row r="22">
@@ -2137,7 +2137,7 @@
         <v>68</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>11180.177</v>
+        <v>11186.877</v>
       </c>
     </row>
     <row r="23">
@@ -2148,7 +2148,7 @@
         <v>70</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>7078.984</v>
+        <v>7082.326</v>
       </c>
     </row>
     <row r="24">
@@ -2159,7 +2159,7 @@
         <v>72</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>22345.083</v>
+        <v>22345.578</v>
       </c>
     </row>
     <row r="25">
@@ -2170,7 +2170,7 @@
         <v>74</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>7546.631</v>
+        <v>7568.159</v>
       </c>
     </row>
     <row r="26">
@@ -2181,7 +2181,7 @@
         <v>76</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>3864.07</v>
+        <v>3866.215</v>
       </c>
     </row>
     <row r="27">
@@ -2192,7 +2192,7 @@
         <v>78</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>4062.949</v>
+        <v>4079.874</v>
       </c>
     </row>
     <row r="28">
@@ -2203,7 +2203,7 @@
         <v>80</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>676.917</v>
+        <v>680.798</v>
       </c>
     </row>
     <row r="29">
@@ -2214,7 +2214,7 @@
         <v>82</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>4851.513</v>
+        <v>4854.297</v>
       </c>
     </row>
     <row r="30">
@@ -2225,7 +2225,7 @@
         <v>84</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>3948.647</v>
+        <v>3953.122</v>
       </c>
     </row>
     <row r="31">
@@ -2236,7 +2236,7 @@
         <v>86</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>3351.699</v>
+        <v>3355.6</v>
       </c>
     </row>
   </sheetData>
@@ -2274,7 +2274,7 @@
         <v>34</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>23616.676</v>
+        <v>24052.987</v>
       </c>
     </row>
     <row r="3">
@@ -2285,7 +2285,7 @@
         <v>32</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>20052.968</v>
+        <v>21953.946</v>
       </c>
     </row>
     <row r="4">
@@ -2296,7 +2296,7 @@
         <v>28</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>25827.046</v>
+        <v>26502.356</v>
       </c>
     </row>
     <row r="5">
@@ -2307,7 +2307,7 @@
         <v>36</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>7518.04</v>
+        <v>7523.408</v>
       </c>
     </row>
     <row r="6">
@@ -2318,7 +2318,7 @@
         <v>48</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>6932.992</v>
+        <v>7132.191</v>
       </c>
     </row>
     <row r="7">
@@ -2329,7 +2329,7 @@
         <v>50</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>8066.116</v>
+        <v>10067.056</v>
       </c>
     </row>
     <row r="8">
@@ -2340,7 +2340,7 @@
         <v>44</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>7521.647</v>
+        <v>7825.57</v>
       </c>
     </row>
     <row r="9">
@@ -2351,7 +2351,7 @@
         <v>38</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>7230.279</v>
+        <v>7327.271</v>
       </c>
     </row>
     <row r="10">
@@ -2362,29 +2362,29 @@
         <v>46</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>5541.492</v>
+        <v>5788.599</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>11483.493</v>
+        <v>8593.374</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>6683.333</v>
+        <v>11483.549</v>
       </c>
     </row>
     <row r="13">
@@ -2395,7 +2395,7 @@
         <v>42</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>3582.021</v>
+        <v>3860.991</v>
       </c>
     </row>
     <row r="14">
@@ -2428,7 +2428,7 @@
         <v>64</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>3178.585</v>
+        <v>4067.092</v>
       </c>
     </row>
     <row r="17">
@@ -2439,7 +2439,7 @@
         <v>78</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>1931.294</v>
+        <v>1956.734</v>
       </c>
     </row>
     <row r="18">
@@ -2461,7 +2461,7 @@
         <v>40</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>5857.158</v>
+        <v>5910.352</v>
       </c>
     </row>
     <row r="20">
@@ -2472,7 +2472,7 @@
         <v>54</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>3692.137</v>
+        <v>3692.202</v>
       </c>
     </row>
     <row r="21">
@@ -2483,7 +2483,7 @@
         <v>62</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>5378.009</v>
+        <v>5495.523</v>
       </c>
     </row>
     <row r="22">
@@ -2494,7 +2494,7 @@
         <v>70</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>3695.613</v>
+        <v>4142.692</v>
       </c>
     </row>
     <row r="23">
@@ -2505,29 +2505,29 @@
         <v>56</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>1464.553</v>
+        <v>1530.153</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>3269.8</v>
+        <v>4533.79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>4347.427</v>
+        <v>3298.454</v>
       </c>
     </row>
     <row r="26">
@@ -2549,7 +2549,7 @@
         <v>92</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>2138.56</v>
+        <v>2202.726</v>
       </c>
     </row>
     <row r="28">
@@ -2560,7 +2560,7 @@
         <v>82</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>1755.803</v>
+        <v>1778.054</v>
       </c>
     </row>
     <row r="29">
@@ -2571,7 +2571,7 @@
         <v>94</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>2310.399</v>
+        <v>2318.693</v>
       </c>
     </row>
     <row r="30">
@@ -2582,7 +2582,7 @@
         <v>76</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>1259.148</v>
+        <v>1267.826</v>
       </c>
     </row>
     <row r="31">
@@ -2631,7 +2631,7 @@
         <v>28</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>129397.464</v>
+        <v>129402.049</v>
       </c>
     </row>
     <row r="3">
@@ -2642,7 +2642,7 @@
         <v>34</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>56131.485</v>
+        <v>56179.166</v>
       </c>
     </row>
     <row r="4">
@@ -2675,7 +2675,7 @@
         <v>30</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>104603.768</v>
+        <v>104676.367</v>
       </c>
     </row>
     <row r="7">
@@ -2686,7 +2686,7 @@
         <v>42</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>24547.716</v>
+        <v>24627.265</v>
       </c>
     </row>
     <row r="8">
@@ -2708,7 +2708,7 @@
         <v>38</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>27132.855</v>
+        <v>27137.09</v>
       </c>
     </row>
     <row r="10">
@@ -2719,7 +2719,7 @@
         <v>60</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>40163.892</v>
+        <v>40365.663</v>
       </c>
     </row>
     <row r="11">
@@ -2730,7 +2730,7 @@
         <v>40</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>42406.9</v>
+        <v>42435.055</v>
       </c>
     </row>
     <row r="12">
@@ -2752,7 +2752,7 @@
         <v>44</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>18403.381</v>
+        <v>18404.081</v>
       </c>
     </row>
     <row r="14">
@@ -2763,7 +2763,7 @@
         <v>64</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>14620.337</v>
+        <v>14653.534</v>
       </c>
     </row>
     <row r="15">
@@ -2796,7 +2796,7 @@
         <v>58</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>12385.919</v>
+        <v>12387.324</v>
       </c>
     </row>
     <row r="18">
@@ -2829,7 +2829,7 @@
         <v>66</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>6149.572</v>
+        <v>6475.407</v>
       </c>
     </row>
     <row r="21">
@@ -2851,7 +2851,7 @@
         <v>82</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>7966.278</v>
+        <v>8003.829</v>
       </c>
     </row>
     <row r="23">
@@ -2862,7 +2862,7 @@
         <v>86</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>7342.893</v>
+        <v>7379.224</v>
       </c>
     </row>
     <row r="24">
@@ -2917,7 +2917,7 @@
         <v>70</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>6108.522</v>
+        <v>6158.141</v>
       </c>
     </row>
     <row r="29">
@@ -2988,7 +2988,7 @@
         <v>28</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>47170.04</v>
+        <v>47467.248</v>
       </c>
     </row>
     <row r="3">
@@ -2999,7 +2999,7 @@
         <v>34</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>28949.137</v>
+        <v>29015.514</v>
       </c>
     </row>
     <row r="4">
@@ -3010,7 +3010,7 @@
         <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>27697.279</v>
+        <v>27774.594</v>
       </c>
     </row>
     <row r="5">
@@ -3021,7 +3021,7 @@
         <v>36</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>11482.52</v>
+        <v>11598.832</v>
       </c>
     </row>
     <row r="6">
@@ -3032,7 +3032,7 @@
         <v>38</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>12558.45</v>
+        <v>12600.385</v>
       </c>
     </row>
     <row r="7">
@@ -3043,7 +3043,7 @@
         <v>44</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>13569.425</v>
+        <v>13623.756</v>
       </c>
     </row>
     <row r="8">
@@ -3054,7 +3054,7 @@
         <v>48</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>8779.12</v>
+        <v>8801.38</v>
       </c>
     </row>
     <row r="9">
@@ -3065,7 +3065,7 @@
         <v>56</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3975.25</v>
+        <v>3991.915</v>
       </c>
     </row>
     <row r="10">
@@ -3076,7 +3076,7 @@
         <v>46</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>9135.079</v>
+        <v>9144.666</v>
       </c>
     </row>
     <row r="11">
@@ -3087,7 +3087,7 @@
         <v>60</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>10348.777</v>
+        <v>10351.176</v>
       </c>
     </row>
     <row r="12">
@@ -3098,7 +3098,7 @@
         <v>58</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>7443.12</v>
+        <v>7449.458</v>
       </c>
     </row>
     <row r="13">
@@ -3109,7 +3109,7 @@
         <v>42</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>5456.372</v>
+        <v>5469.808</v>
       </c>
     </row>
     <row r="14">
@@ -3120,7 +3120,7 @@
         <v>50</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>6508.943</v>
+        <v>6515.47</v>
       </c>
     </row>
     <row r="15">
@@ -3131,7 +3131,7 @@
         <v>80</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1524.51</v>
+        <v>1526.639</v>
       </c>
     </row>
     <row r="16">
@@ -3142,7 +3142,7 @@
         <v>68</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>10689.111</v>
+        <v>10689.586</v>
       </c>
     </row>
     <row r="17">
@@ -3153,7 +3153,7 @@
         <v>78</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>4319.968</v>
+        <v>4328.264</v>
       </c>
     </row>
     <row r="18">
@@ -3164,7 +3164,7 @@
         <v>66</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>4267.068</v>
+        <v>4267.369</v>
       </c>
     </row>
     <row r="19">
@@ -3175,7 +3175,7 @@
         <v>64</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>3510.368</v>
+        <v>3539.302</v>
       </c>
     </row>
     <row r="20">
@@ -3186,7 +3186,7 @@
         <v>76</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>3854.426</v>
+        <v>3857.192</v>
       </c>
     </row>
     <row r="21">
@@ -3197,7 +3197,7 @@
         <v>88</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>5041.489</v>
+        <v>5043.015</v>
       </c>
     </row>
     <row r="22">
@@ -3208,7 +3208,7 @@
         <v>74</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>5259.917</v>
+        <v>5264.856</v>
       </c>
     </row>
     <row r="23">
@@ -3219,7 +3219,7 @@
         <v>54</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>2894.589</v>
+        <v>2901.219</v>
       </c>
     </row>
     <row r="24">
@@ -3230,7 +3230,7 @@
         <v>70</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>4196.909</v>
+        <v>4201.609</v>
       </c>
     </row>
     <row r="25">
@@ -3241,7 +3241,7 @@
         <v>82</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>4028.049</v>
+        <v>4038.186</v>
       </c>
     </row>
     <row r="26">
@@ -3252,7 +3252,7 @@
         <v>92</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>2995.37</v>
+        <v>3001.812</v>
       </c>
     </row>
     <row r="27">
@@ -3263,7 +3263,7 @@
         <v>84</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>2786.497</v>
+        <v>2791.158</v>
       </c>
     </row>
     <row r="28">
@@ -3274,7 +3274,7 @@
         <v>40</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>1568.821</v>
+        <v>1570.379</v>
       </c>
     </row>
     <row r="29">
@@ -3285,7 +3285,7 @@
         <v>86</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>2243.489</v>
+        <v>2255.433</v>
       </c>
     </row>
     <row r="30">
@@ -3296,7 +3296,7 @@
         <v>62</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>3628.887</v>
+        <v>3629.482</v>
       </c>
     </row>
     <row r="31">
@@ -3307,7 +3307,7 @@
         <v>30</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>1437.182</v>
+        <v>1440.324</v>
       </c>
     </row>
   </sheetData>
@@ -4059,7 +4059,7 @@
         <v>28</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>16769.398</v>
+        <v>18325.245</v>
       </c>
     </row>
     <row r="3">
@@ -4070,7 +4070,7 @@
         <v>36</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5655.396</v>
+        <v>5869.587</v>
       </c>
     </row>
     <row r="4">
@@ -4081,7 +4081,7 @@
         <v>34</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>11561.977</v>
+        <v>11608.379</v>
       </c>
     </row>
     <row r="5">
@@ -4092,7 +4092,7 @@
         <v>32</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>13529.988</v>
+        <v>13644.827</v>
       </c>
     </row>
     <row r="6">
@@ -4103,7 +4103,7 @@
         <v>52</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>31005.531</v>
+        <v>31005.709</v>
       </c>
     </row>
     <row r="7">
@@ -4114,7 +4114,7 @@
         <v>38</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>6842.267</v>
+        <v>6859.569</v>
       </c>
     </row>
     <row r="8">
@@ -4125,7 +4125,7 @@
         <v>42</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>8765.86</v>
+        <v>8769.218</v>
       </c>
     </row>
     <row r="9">
@@ -4147,7 +4147,7 @@
         <v>30</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>7543.523</v>
+        <v>7546.964</v>
       </c>
     </row>
     <row r="11">
@@ -4158,7 +4158,7 @@
         <v>44</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4638.683</v>
+        <v>4655.051</v>
       </c>
     </row>
     <row r="12">
@@ -4169,7 +4169,7 @@
         <v>62</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>9213.353</v>
+        <v>9222.547</v>
       </c>
     </row>
     <row r="13">
@@ -4191,7 +4191,7 @@
         <v>64</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>2478.717</v>
+        <v>2482.412</v>
       </c>
     </row>
     <row r="15">
@@ -4202,7 +4202,7 @@
         <v>54</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>2075.28</v>
+        <v>2082.64</v>
       </c>
     </row>
     <row r="16">
@@ -4213,7 +4213,7 @@
         <v>60</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4759.086</v>
+        <v>4761.36</v>
       </c>
     </row>
     <row r="17">
@@ -4224,7 +4224,7 @@
         <v>50</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>3321.398</v>
+        <v>3340.551</v>
       </c>
     </row>
     <row r="18">
@@ -4235,7 +4235,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>2199.872</v>
+        <v>2211.075</v>
       </c>
     </row>
     <row r="19">
@@ -4246,7 +4246,7 @@
         <v>46</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>1894.61</v>
+        <v>1907.327</v>
       </c>
     </row>
     <row r="20">
@@ -4268,7 +4268,7 @@
         <v>66</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>3830.833</v>
+        <v>3830.911</v>
       </c>
     </row>
     <row r="22">
@@ -4279,29 +4279,29 @@
         <v>48</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>2117.174</v>
+        <v>2128.479</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>5402.148</v>
+        <v>3230.221</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B24" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>3088.21</v>
+        <v>5402.213</v>
       </c>
     </row>
     <row r="25">
@@ -4312,7 +4312,7 @@
         <v>70</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>4321.281</v>
+        <v>4351.255</v>
       </c>
     </row>
     <row r="26">
@@ -4323,7 +4323,7 @@
         <v>78</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>1999.743</v>
+        <v>2025.619</v>
       </c>
     </row>
     <row r="27">
@@ -4334,29 +4334,29 @@
         <v>74</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>1697.608</v>
+        <v>1699.488</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>1140.812</v>
+        <v>793.401</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>766.408</v>
+        <v>1144.77</v>
       </c>
     </row>
     <row r="30">
@@ -4367,7 +4367,7 @@
         <v>84</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>1557.611</v>
+        <v>1561.19</v>
       </c>
     </row>
     <row r="31">
@@ -4378,7 +4378,7 @@
         <v>82</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>1563.83</v>
+        <v>1566.226</v>
       </c>
     </row>
   </sheetData>
@@ -4416,7 +4416,7 @@
         <v>28</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9933.579</v>
+        <v>9934.687</v>
       </c>
     </row>
     <row r="3">
@@ -4460,7 +4460,7 @@
         <v>34</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>9895.151</v>
+        <v>9895.34</v>
       </c>
     </row>
     <row r="7">
@@ -4493,7 +4493,7 @@
         <v>32</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>4339.492</v>
+        <v>4339.711</v>
       </c>
     </row>
     <row r="10">
@@ -4548,7 +4548,7 @@
         <v>66</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>7927.808</v>
+        <v>8009.451</v>
       </c>
     </row>
     <row r="15">
@@ -4614,7 +4614,7 @@
         <v>48</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2579.647</v>
+        <v>2579.867</v>
       </c>
     </row>
     <row r="21">
@@ -4713,7 +4713,7 @@
         <v>86</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>1823.62</v>
+        <v>1823.708</v>
       </c>
     </row>
     <row r="30">
